--- a/backend/src/db/demo-docs/measurements-cropped-fleece-hoodie.xlsx
+++ b/backend/src/db/demo-docs/measurements-cropped-fleece-hoodie.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Poly Spandex Blend</t>
+          <t>88% Polyester 12% Spandex</t>
         </is>
       </c>
     </row>
@@ -589,19 +589,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="E10" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="F10" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="G10" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="H10" s="5" t="n">
         <v>47</v>
       </c>
     </row>
@@ -618,19 +621,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>53</v>
       </c>
       <c r="F11" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="G11" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="H11" s="5" t="n">
         <v>57</v>
       </c>
     </row>
@@ -647,19 +653,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>55</v>
       </c>
       <c r="F12" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="G12" s="5" t="n">
         <v>57</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="H12" s="5" t="n">
         <v>59</v>
       </c>
     </row>
@@ -683,7 +692,7 @@
         <v>28.5</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>31.5</v>
+        <v>29.5</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>30.5</v>
@@ -715,7 +724,7 @@
         <v>37.5</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>40</v>
@@ -740,19 +749,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="G15" s="5" t="n">
         <v>34.5</v>
       </c>
-      <c r="E15" s="5" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="G15" s="5" t="n">
+      <c r="H15" s="5" t="n">
         <v>35.5</v>
       </c>
     </row>
@@ -769,19 +781,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E16" s="5" t="n">
         <v>22.5</v>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="F16" s="5" t="n">
         <v>23.5</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="G16" s="5" t="n">
         <v>24.5</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="H16" s="5" t="n">
         <v>25.5</v>
       </c>
     </row>
@@ -837,7 +852,7 @@
         <v>16.5</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>17.5</v>
